--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104556_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104556_W11.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7281</v>
+        <v>8.139799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1116</v>
+        <v>8.010400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3835</v>
+        <v>0.1295</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6951</v>
+        <v>5.6793</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3578</v>
+        <v>-1.3585</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0529</v>
+        <v>7.0378</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6403</v>
+        <v>6.5888</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.1584</v>
+        <v>-2.1761</v>
       </c>
       <c r="L2" t="n">
-        <v>8.7986</v>
+        <v>8.764900000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9452</v>
+        <v>-0.9095</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8006</v>
+        <v>0.8176</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7458</v>
+        <v>-1.7271</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7648</v>
+        <v>-0.333</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5383</v>
+        <v>0.4294</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2264</v>
+        <v>-0.7625</v>
       </c>
       <c r="V2" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7787</v>
+        <v>5.6078</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6067</v>
+        <v>5.5198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1719</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0892</v>
+        <v>6.0895</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3059</v>
+        <v>4.2971</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7833</v>
+        <v>1.7924</v>
       </c>
       <c r="J3" t="n">
-        <v>6.704</v>
+        <v>6.6687</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6467</v>
+        <v>3.623</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0573</v>
+        <v>3.0458</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6148</v>
+        <v>-0.5792</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.274</v>
+        <v>-1.2533</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9969</v>
+        <v>-0.1599</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6079</v>
+        <v>0.3597</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.389</v>
+        <v>-0.5196</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.221</v>
+        <v>-1.2324</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1284</v>
+        <v>-0.1429</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8767</v>
+        <v>4.0419</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9606</v>
+        <v>4.0946</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0527</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2422</v>
+        <v>4.2253</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6132</v>
+        <v>3.6076</v>
       </c>
       <c r="I4" t="n">
-        <v>0.629</v>
+        <v>0.6177</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4493</v>
+        <v>4.4061</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7809</v>
+        <v>2.7612</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6684</v>
+        <v>1.645</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2071</v>
+        <v>-0.1808</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8324</v>
+        <v>0.8465</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1542</v>
+        <v>0.3417</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5263</v>
+        <v>0.7175</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.372</v>
+        <v>-0.3758</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9727</v>
+        <v>1.8538</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5817</v>
+        <v>0.5003</v>
       </c>
       <c r="F5" t="n">
-        <v>0.391</v>
+        <v>1.3535</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1882</v>
+        <v>1.5995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7602</v>
+        <v>1.2746</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9485</v>
+        <v>0.3248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1834</v>
+        <v>2.5539</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7517</v>
+        <v>1.6231</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3716</v>
+        <v>-0.9544</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1749</v>
+        <v>0.3438</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1967</v>
+        <v>-1.2982</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6293</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3101</v>
+        <v>0.1617</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5889</v>
+        <v>0.4504</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2789</v>
+        <v>-0.2887</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4387</v>
+        <v>1.0032</v>
       </c>
       <c r="W5" t="n">
-        <v>3.4387</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.0032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7718</v>
+        <v>1.1868</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3227</v>
+        <v>1.0159</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0945</v>
+        <v>0.1709</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5864</v>
+        <v>-1.1733</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2639</v>
+        <v>0.7719</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3225</v>
+        <v>-1.9453</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5716</v>
+        <v>0.1707</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6365</v>
+        <v>-0.7601</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9852</v>
+        <v>-1.3441</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3288</v>
+        <v>-0.1588</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.314</v>
+        <v>-1.1852</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9034</v>
+        <v>0.5274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3992</v>
+        <v>1.0611</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5042</v>
+        <v>-0.5337</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9961</v>
+        <v>3.4262</v>
       </c>
       <c r="W6" t="n">
+        <v>3.4262</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.9961</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7714</v>
+        <v>0.6987</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8697</v>
+        <v>2.801</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0984</v>
+        <v>-2.1023</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2906</v>
+        <v>0.2931</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0693</v>
+        <v>-0.0689</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3599</v>
+        <v>0.3621</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0704</v>
+        <v>2.0532</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3565</v>
+        <v>0.348</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7798</v>
+        <v>-1.7601</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.039</v>
+        <v>-0.1195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1603</v>
+        <v>0.1136</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1993</v>
+        <v>-0.2331</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.125</v>
+        <v>0.0927</v>
       </c>
       <c r="E8" t="n">
-        <v>1.251</v>
+        <v>0.3917</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.126</v>
+        <v>-0.299</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8913</v>
+        <v>-0.9689</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0043</v>
+        <v>0.491</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8956</v>
+        <v>-1.4599</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6885</v>
+        <v>-0.1808</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1314</v>
+        <v>0.5343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5798</v>
+        <v>-0.7881</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1272</v>
+        <v>-0.0433</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4526</v>
+        <v>-0.7447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8822</v>
+        <v>0.0615</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0162</v>
+        <v>0.0278</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.134</v>
+        <v>0.0338</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.5463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0497</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1627</v>
+        <v>0.649</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2124</v>
+        <v>-1.3229</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9689</v>
+        <v>-0.8853</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4891</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4581</v>
+        <v>-0.8937</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1749</v>
+        <v>0.6748</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.1239</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.794</v>
+        <v>-1.5601</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0477</v>
+        <v>-0.1155</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7463</v>
+        <v>-1.4446</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
+        <v>-0.4553</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1382</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.3562</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.5447</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.4537</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.0808</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.2087</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1279</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.5463</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.5463</v>
-      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8919</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0291</v>
+        <v>0.0851</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8628</v>
+        <v>-0.8224</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2984</v>
+        <v>-0.2951</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2771</v>
+        <v>-0.2758</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1066</v>
+        <v>0.1062</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.405</v>
+        <v>-0.4012</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.206</v>
+        <v>-0.0569</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4076</v>
+        <v>-0.9316</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.274</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1337</v>
+        <v>-0.9987</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5142</v>
+        <v>-0.5158</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.834</v>
+        <v>-0.833</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3198</v>
+        <v>0.3172</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5275</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0417</v>
+        <v>-1.0314</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6666</v>
+        <v>-0.1881</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3188</v>
+        <v>-0.195</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4293</v>
+        <v>-2.3446</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0477</v>
+        <v>0.2318</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.477</v>
+        <v>-2.5764</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.636</v>
+        <v>-0.6324</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2035</v>
+        <v>0.1985</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8396</v>
+        <v>-0.8308</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4257</v>
+        <v>-0.4368</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7242</v>
+        <v>-0.7347</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2104</v>
+        <v>-0.1956</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9277</v>
+        <v>0.9331</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6435</v>
+        <v>0.7156</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3126</v>
+        <v>0.5108</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3309</v>
+        <v>0.2047</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.2459</v>
+        <v>16.934</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9659</v>
+        <v>23.3667</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.7204</v>
+        <v>-6.4325</v>
       </c>
       <c r="G13" t="n">
-        <v>13.4065</v>
+        <v>13.4159</v>
       </c>
       <c r="H13" t="n">
-        <v>8.101900000000001</v>
+        <v>8.1129</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3043</v>
+        <v>5.303</v>
       </c>
       <c r="J13" t="n">
-        <v>23.341</v>
+        <v>23.1204</v>
       </c>
       <c r="K13" t="n">
-        <v>6.069199999999999</v>
+        <v>5.965200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>17.2716</v>
+        <v>17.1552</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.9346</v>
+        <v>-9.704499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>2.0328</v>
+        <v>2.147800000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.9673</v>
+        <v>-11.8521</v>
       </c>
       <c r="P13" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.6579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3325</v>
+        <v>1.0237</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4328</v>
+        <v>4.1552</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1002</v>
+        <v>-3.1318</v>
       </c>
       <c r="V13" t="n">
-        <v>2.506799999999999</v>
+        <v>2.4944</v>
       </c>
       <c r="W13" t="n">
-        <v>9.802099999999999</v>
+        <v>9.748699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.295500000000001</v>
+        <v>-7.254099999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8391</v>
+        <v>6.5602</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3112</v>
+        <v>6.6188</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4722</v>
+        <v>-0.0586</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1788</v>
+        <v>4.1648</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1686</v>
+        <v>-0.1803</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3475</v>
+        <v>4.3451</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3844</v>
+        <v>7.3418</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4462</v>
+        <v>0.4234</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9382</v>
+        <v>6.9184</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2056</v>
+        <v>-3.177</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.5908</v>
+        <v>-2.5733</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7234</v>
+        <v>0.0068</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0998</v>
+        <v>0.2574</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6236</v>
+        <v>-0.2505</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
-        <v>1.5425</v>
+        <v>1.5479</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.845</v>
+        <v>3.5478</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7896</v>
+        <v>4.4075</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9446</v>
+        <v>-0.8598</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5568</v>
+        <v>4.551</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0534</v>
+        <v>3.0449</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5034</v>
+        <v>1.5061</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3694</v>
+        <v>5.3507</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9438</v>
+        <v>2.9303</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4256</v>
+        <v>2.4204</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8126</v>
+        <v>-0.7997</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3563</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5958</v>
+        <v>0.2437</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1802</v>
+        <v>-1.457</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5569</v>
+        <v>1.3038</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7371</v>
+        <v>-2.7608</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.7179</v>
+        <v>-2.7098</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2035</v>
+        <v>-2.1975</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J16" t="n">
-        <v>0.834</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3995</v>
+        <v>-1.4069</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2336</v>
+        <v>2.2189</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.552</v>
+        <v>-3.5218</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.748</v>
+        <v>-2.7312</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8157</v>
+        <v>0.5212</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7229</v>
+        <v>0.4918</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0294</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9725</v>
+        <v>-1.8489</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1999</v>
+        <v>0.5995</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.1724</v>
+        <v>-2.4484</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.3544</v>
+        <v>-2.2088</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.6939</v>
+        <v>-0.0261</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6605</v>
+        <v>-2.1827</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.3674</v>
+        <v>1.2853</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.5913</v>
+        <v>0.9513</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2239</v>
+        <v>0.334</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.987</v>
+        <v>-3.4941</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1026</v>
+        <v>-0.9774</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8844</v>
+        <v>-2.5168</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4158</v>
+        <v>0.5664</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1966</v>
+        <v>0.5011</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6125</v>
+        <v>0.0653</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1173</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3707</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.125</v>
+        <v>-1.8936</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6425999999999999</v>
+        <v>1.9368</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7676</v>
+        <v>-3.8304</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2029</v>
+        <v>-5.349</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0304</v>
+        <v>-3.699</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1725</v>
+        <v>-1.65</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3223</v>
+        <v>-2.3836</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9626</v>
+        <v>-2.607</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3596</v>
+        <v>0.2234</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.5251</v>
+        <v>-2.9654</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.993</v>
+        <v>-1.092</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5321</v>
+        <v>-1.8734</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2801</v>
+        <v>-0.3382</v>
       </c>
       <c r="T18" t="n">
-        <v>0.496</v>
+        <v>-0.0375</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.216</v>
+        <v>-0.3006</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>3.1107</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>4.3579</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5928</v>
+        <v>-3.119</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3934</v>
+        <v>-2.0391</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1994</v>
+        <v>-1.0798</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1482</v>
+        <v>-0.011</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5729</v>
+        <v>0.1123</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5753</v>
+        <v>-0.1233</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.221</v>
+        <v>0.1293</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5093</v>
+        <v>-0.1314</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7117</v>
+        <v>0.2607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9272</v>
+        <v>-0.1403</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0636</v>
+        <v>0.2437</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8636</v>
+        <v>-0.384</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.711</v>
+        <v>0.1637</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1724</v>
+        <v>0.5177</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5387</v>
+        <v>-0.354</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4141</v>
+        <v>-3.7268</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-1.5479</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4141</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6981</v>
+        <v>-3.2721</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3732</v>
+        <v>-1.2826</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3249</v>
+        <v>-1.9894</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0136</v>
+        <v>-2.1445</v>
       </c>
       <c r="H20" t="n">
-        <v>0.117</v>
+        <v>-0.5716</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1306</v>
+        <v>-1.5729</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1431</v>
+        <v>-1.229</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1181</v>
+        <v>-0.5139</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2612</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1567</v>
+        <v>-0.9155</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2351</v>
+        <v>-0.0578</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.8578</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4104</v>
+        <v>-0.4054</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1603</v>
+        <v>-0.0536</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5707</v>
+        <v>-0.3518</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.7278</v>
+        <v>-1.405</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.5425</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0212</v>
+        <v>-4.0824</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0639</v>
+        <v>-1.9156</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9572</v>
+        <v>-2.1668</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4607</v>
+        <v>-3.5986</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9019</v>
+        <v>-3.0183</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5588</v>
+        <v>-0.5802</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.82</v>
+        <v>0.0679</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1456</v>
+        <v>-1.7107</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6744</v>
+        <v>1.7786</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6407</v>
+        <v>-3.6665</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7563</v>
+        <v>-1.3077</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8844</v>
+        <v>-2.3588</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5588</v>
+        <v>0.3679</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8903</v>
+        <v>0.4616</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3315</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3461</v>
+        <v>2.1075</v>
       </c>
       <c r="W21" t="n">
+        <v>2.1075</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-2.3461</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3794</v>
+        <v>-4.5783</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4271</v>
+        <v>-1.9436</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9523</v>
+        <v>-2.6346</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5768</v>
+        <v>-2.6595</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0143</v>
+        <v>-0.6783</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5626</v>
+        <v>-1.9812</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1215</v>
+        <v>-0.8401</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6908</v>
+        <v>0.0689</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8123</v>
+        <v>-0.909</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.6983</v>
+        <v>-1.8194</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3234</v>
+        <v>-0.7472</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3749</v>
+        <v>-1.0722</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9488</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0251</v>
+        <v>-0.7398</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1331</v>
+        <v>0.0346</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1582</v>
+        <v>-0.7744</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1212</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1212</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9607</v>
+        <v>-5.3042</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5224</v>
+        <v>-1.2529</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4383</v>
+        <v>-4.0513</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6675</v>
+        <v>-3.4505</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.8991</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9805</v>
+        <v>-2.5514</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8317</v>
+        <v>-0.8298</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0693</v>
+        <v>-0.1519</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.901</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8357</v>
+        <v>-2.6207</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0795</v>
+        <v>-1.8734</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1079</v>
+        <v>0.2554</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>0.7151</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5514</v>
+        <v>-0.4596</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-2.3367</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.2458</v>
+        <v>-15.4475</v>
       </c>
       <c r="E24" t="n">
-        <v>6.720199999999999</v>
+        <v>6.432599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.966</v>
+        <v>-21.8799</v>
       </c>
       <c r="G24" t="n">
-        <v>-13.4064</v>
+        <v>-13.4159</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.1021</v>
+        <v>-8.113000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.3043</v>
+        <v>-5.3028</v>
       </c>
       <c r="J24" t="n">
-        <v>9.9346</v>
+        <v>9.704499999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0327</v>
+        <v>-2.147900000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>11.9673</v>
+        <v>11.8523</v>
       </c>
       <c r="M24" t="n">
-        <v>-23.3409</v>
+        <v>-23.1204</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.0693</v>
+        <v>-5.965300000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-17.2717</v>
+        <v>-17.1552</v>
       </c>
       <c r="P24" t="n">
-        <v>0.000100000000000211</v>
+        <v>9.999999999968368e-05</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R24" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3325</v>
+        <v>0.4631000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1001</v>
+        <v>3.1319</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.4329</v>
+        <v>-2.6685</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.506699999999999</v>
+        <v>-2.4944</v>
       </c>
       <c r="W24" t="n">
-        <v>7.295500000000001</v>
+        <v>7.254299999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.802199999999999</v>
+        <v>-9.7486</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104556_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104556_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>1.0032</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.254099999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>1.5479</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104556_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.7486</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
